--- a/data/trans_dic/P2A_psíq_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,99</t>
+          <t>1,24; 3,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,88</t>
+          <t>2,25; 4,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,06</t>
+          <t>1,01; 2,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,51</t>
+          <t>2,5; 5,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,38</t>
+          <t>1,04; 2,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,03</t>
+          <t>2,14; 4,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,55</t>
+          <t>1,51; 3,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,95</t>
+          <t>3,1; 5,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,44</t>
+          <t>1,3; 2,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,92</t>
+          <t>2,41; 3,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,93</t>
+          <t>1,54; 2,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,81</t>
+          <t>3,12; 4,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,01</t>
+          <t>0,22; 0,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,89</t>
+          <t>0,79; 1,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,32</t>
+          <t>0,4; 1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,43</t>
+          <t>1,11; 2,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,24</t>
+          <t>0,32; 1,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,2</t>
+          <t>1,03; 2,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,08</t>
+          <t>0,94; 2,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 35,9</t>
+          <t>2,39; 33,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,94</t>
+          <t>0,39; 0,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,82</t>
+          <t>1,04; 1,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,47</t>
+          <t>0,77; 1,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 22,64</t>
+          <t>1,95; 21,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,27</t>
+          <t>0,43; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,0</t>
+          <t>1,24; 4,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,89</t>
+          <t>0,64; 3,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,62</t>
+          <t>0,67; 3,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,88</t>
+          <t>0,35; 2,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,91</t>
+          <t>1,25; 3,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,58</t>
+          <t>0,36; 1,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,6</t>
+          <t>0,74; 2,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,27</t>
+          <t>0,27; 1,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,18</t>
+          <t>1,52; 3,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,28</t>
+          <t>0,61; 1,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,42</t>
+          <t>1,37; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,35</t>
+          <t>0,65; 1,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,72</t>
+          <t>1,51; 2,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,59</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,62</t>
+          <t>1,65; 2,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,14</t>
+          <t>1,24; 2,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 25,46</t>
+          <t>2,7; 25,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,31</t>
+          <t>0,82; 1,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,35</t>
+          <t>1,61; 2,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,64</t>
+          <t>1,03; 1,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 15,38</t>
+          <t>2,32; 15,33</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12755; 30886</t>
+          <t>12765; 31049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22259; 47551</t>
+          <t>21914; 47501</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8144; 23086</t>
+          <t>7624; 22368</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12701; 28377</t>
+          <t>12889; 28778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13452; 31305</t>
+          <t>13622; 32016</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27656; 53857</t>
+          <t>28656; 57538</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15384; 35306</t>
+          <t>15033; 34603</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22040; 37370</t>
+          <t>23405; 38276</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30572; 57356</t>
+          <t>30530; 55557</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53527; 90654</t>
+          <t>55756; 91610</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26903; 51289</t>
+          <t>26895; 50944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38762; 61083</t>
+          <t>39577; 61411</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3675; 17125</t>
+          <t>3722; 16528</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15765; 37156</t>
+          <t>15436; 36575</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9359; 27444</t>
+          <t>8375; 25207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23285; 55720</t>
+          <t>25537; 58597</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5891; 19681</t>
+          <t>5156; 19888</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18345; 38638</t>
+          <t>18074; 39162</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18437; 41400</t>
+          <t>18701; 41560</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53489; 803325</t>
+          <t>53523; 746728</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12520; 30952</t>
+          <t>12687; 30663</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38487; 67610</t>
+          <t>38877; 67580</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29256; 59903</t>
+          <t>31368; 61181</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89057; 1025074</t>
+          <t>88471; 979568</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4556</t>
+          <t>0; 4607</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2065; 15715</t>
+          <t>2081; 14983</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7034</t>
+          <t>0; 7245</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7629; 25879</t>
+          <t>8008; 26273</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3163; 13750</t>
+          <t>3036; 14855</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3811; 16589</t>
+          <t>3061; 15706</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1935; 10339</t>
+          <t>1943; 10976</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9249; 25812</t>
+          <t>8288; 23630</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3949; 16242</t>
+          <t>3673; 15308</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7971; 24419</t>
+          <t>6947; 24671</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3020; 13905</t>
+          <t>2925; 14132</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19365; 41566</t>
+          <t>19851; 44061</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19763; 41995</t>
+          <t>20150; 42995</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47549; 82701</t>
+          <t>46786; 84877</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21686; 45478</t>
+          <t>21898; 44824</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52826; 93891</t>
+          <t>52163; 94740</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28622; 53787</t>
+          <t>28386; 53962</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58124; 93043</t>
+          <t>58584; 92279</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43475; 75482</t>
+          <t>43793; 75807</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97332; 930432</t>
+          <t>98642; 927631</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53688; 87187</t>
+          <t>54557; 87362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115084; 163879</t>
+          <t>112158; 160047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71935; 113556</t>
+          <t>71454; 110624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>167210; 1092537</t>
+          <t>164908; 1089601</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,01</t>
+          <t>1,27; 3,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,87</t>
+          <t>2,35; 5,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,97</t>
+          <t>1,1; 3,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,59</t>
+          <t>2,63; 5,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,43</t>
+          <t>0,97; 2,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,3</t>
+          <t>2,09; 4,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,48</t>
+          <t>1,54; 3,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,07</t>
+          <t>3,07; 5,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,37</t>
+          <t>1,27; 2,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,41; 3,96</t>
+          <t>2,41; 4,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,91</t>
+          <t>1,54; 2,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,83</t>
+          <t>3,19; 4,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,98</t>
+          <t>0,22; 1,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,86</t>
+          <t>0,79; 1,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,21</t>
+          <t>0,44; 1,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,56</t>
+          <t>1,38; 2,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,25</t>
+          <t>0,38; 1,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,23</t>
+          <t>1,02; 2,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,09</t>
+          <t>0,9; 2,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 33,37</t>
+          <t>2,33; 3,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,93</t>
+          <t>0,38; 0,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,82</t>
+          <t>1,03; 1,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,51</t>
+          <t>0,78; 1,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 21,63</t>
+          <t>2,01; 2,94</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,11</t>
+          <t>0,39; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,06</t>
+          <t>1,24; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,12</t>
+          <t>0,67; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,42</t>
+          <t>0,64; 3,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,0</t>
+          <t>0,35; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,58</t>
+          <t>1,41; 3,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,49</t>
+          <t>0,38; 1,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,63</t>
+          <t>0,78; 2,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,29</t>
+          <t>0,27; 1,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,37</t>
+          <t>1,54; 3,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,31</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,48</t>
+          <t>1,39; 2,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,33</t>
+          <t>0,65; 1,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,74</t>
+          <t>1,84; 2,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,84; 1,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,6</t>
+          <t>1,65; 2,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,15</t>
+          <t>1,23; 2,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 25,39</t>
+          <t>2,57; 3,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,31</t>
+          <t>0,79; 1,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,29</t>
+          <t>1,63; 2,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,6</t>
+          <t>1,05; 1,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 15,33</t>
+          <t>2,33; 3,08</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19705</t>
+          <t>22551</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>32557</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49533</t>
+          <t>55107</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12765; 31049</t>
+          <t>13099; 31494</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21914; 47501</t>
+          <t>22882; 49155</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7624; 22368</t>
+          <t>8330; 22765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12889; 28778</t>
+          <t>15224; 32179</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13622; 32016</t>
+          <t>12802; 31037</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28656; 57538</t>
+          <t>28010; 54249</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15033; 34603</t>
+          <t>15293; 34627</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23405; 38276</t>
+          <t>25201; 41323</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30530; 55557</t>
+          <t>29922; 56962</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55756; 91610</t>
+          <t>55698; 92884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26895; 50944</t>
+          <t>26875; 52242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39577; 61411</t>
+          <t>44622; 69550</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39077</t>
+          <t>42569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>258168</t>
+          <t>63876</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>297245</t>
+          <t>106445</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3722; 16528</t>
+          <t>3735; 17565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15436; 36575</t>
+          <t>15428; 36968</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8375; 25207</t>
+          <t>9062; 26743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25537; 58597</t>
+          <t>30836; 59439</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5156; 19888</t>
+          <t>5975; 19272</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18074; 39162</t>
+          <t>18008; 38728</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18701; 41560</t>
+          <t>17813; 42020</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53523; 746728</t>
+          <t>50598; 81251</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12687; 30663</t>
+          <t>12356; 31566</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38877; 67580</t>
+          <t>38451; 68534</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31368; 61181</t>
+          <t>31730; 61629</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88471; 979568</t>
+          <t>88314; 129628</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>15977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29210</t>
+          <t>32313</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 5118</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2081; 14983</t>
+          <t>1867; 14892</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7245</t>
+          <t>0; 7388</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8008; 26273</t>
+          <t>8843; 28758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3036; 14855</t>
+          <t>3177; 15470</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3061; 15706</t>
+          <t>2954; 15474</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1943; 10976</t>
+          <t>1931; 11104</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8288; 23630</t>
+          <t>10354; 24808</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3673; 15308</t>
+          <t>3907; 15810</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6947; 24671</t>
+          <t>7302; 24483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2925; 14132</t>
+          <t>3004; 13990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19851; 44061</t>
+          <t>22244; 45117</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>303003</t>
+          <t>112768</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>375988</t>
+          <t>193866</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20150; 42995</t>
+          <t>20555; 44210</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46786; 84877</t>
+          <t>47439; 81341</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21898; 44824</t>
+          <t>21950; 46315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52163; 94740</t>
+          <t>64925; 102464</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28386; 53962</t>
+          <t>28524; 55457</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58584; 92279</t>
+          <t>58640; 93158</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43793; 75807</t>
+          <t>43321; 74206</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>98642; 927631</t>
+          <t>95796; 133577</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>54557; 87362</t>
+          <t>52846; 86909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112158; 160047</t>
+          <t>113785; 166711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71454; 110624</t>
+          <t>72408; 110814</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>164908; 1089601</t>
+          <t>169105; 223413</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_psíq_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2A_psíq_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
